--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -945,22 +945,22 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1048,7 +1048,1339 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -776,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -887,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -937,7 +945,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -965,32 +973,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -998,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1034,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1164,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1159,7 +1175,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1259,7 +1275,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1270,7 +1286,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1347,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1370,7 +1386,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1381,7 +1397,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1458,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1508,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1569,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1619,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1680,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1719,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1714,7 +1730,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1791,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1841,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1902,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1952,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2013,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2063,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2124,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2174,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2235,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2285,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2277,22 +2293,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>07:57</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2325,12 +2341,12 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2344,7 +2360,7 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2369,7 +2385,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2380,7 +2396,1125 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1536,32 +1536,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1569,7 +1573,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1593,33 +1597,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1647,32 +1655,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1680,7 +1692,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1704,17 +1716,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1724,13 +1736,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1758,32 +1774,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -1791,7 +1811,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1815,33 +1835,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1869,32 +1893,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -1902,7 +1930,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1926,33 +1954,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1980,32 +2012,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2013,7 +2049,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2037,33 +2073,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2164,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2202,32 +2242,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2235,7 +2279,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2259,33 +2303,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2394,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2385,7 +2433,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2424,32 +2472,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2457,7 +2509,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2481,17 +2533,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2501,17 +2553,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2624,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2683,7 +2735,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2722,7 +2774,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2794,7 +2846,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2856,22 +2908,22 @@
       <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2904,12 +2956,12 @@
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2923,7 +2975,7 @@
       <c r="T22" s="2" t="inlineStr"/>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2948,7 +3000,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -2967,22 +3019,22 @@
       <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3015,12 +3067,12 @@
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3034,7 +3086,7 @@
       <c r="T23" s="2" t="inlineStr"/>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3059,7 +3111,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3078,7 +3130,7 @@
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3088,7 +3140,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3126,12 +3178,12 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3145,7 +3197,7 @@
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3189,22 +3241,22 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3237,12 +3289,12 @@
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3300,22 +3352,22 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3348,12 +3400,12 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3392,7 +3444,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3411,22 +3463,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3459,12 +3511,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3478,7 +3530,7 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3513,6 +3565,1029 @@
       </c>
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -939,13 +939,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,22 +1053,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1169,13 +1173,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1275,18 +1283,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1359,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1386,18 +1398,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1497,18 +1513,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1617,17 +1637,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1731,22 +1751,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1850,7 +1870,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1865,7 +1885,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1984,7 +2004,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2103,7 +2123,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2333,7 +2353,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2381,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -2394,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2418,17 +2442,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2438,13 +2462,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2494,12 +2522,12 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2509,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2563,7 +2591,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2591,32 +2619,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2624,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2648,17 +2680,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2668,13 +2700,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2813,32 +2849,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2846,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2870,37 +2910,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2928,32 +2968,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2961,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2985,33 +3029,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3039,32 +3087,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3072,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3096,17 +3148,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3116,13 +3168,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3150,32 +3206,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -3183,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3207,17 +3267,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3227,13 +3287,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3261,32 +3325,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3294,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3318,33 +3386,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3372,32 +3444,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -3405,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3429,17 +3505,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3449,13 +3525,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3483,32 +3563,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3516,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3540,33 +3624,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3594,32 +3682,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3627,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3651,37 +3743,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3709,32 +3801,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3742,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3766,17 +3862,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3786,17 +3882,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3911,7 +4007,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3972,7 +4068,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4011,7 +4107,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4026,7 +4122,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4141,7 +4237,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4298,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4256,7 +4352,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4413,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4361,13 +4457,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4528,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4486,22 +4586,22 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4534,12 +4634,12 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4553,43 +4653,737 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr"/>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>—/18</t>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,18 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1298,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1398,22 +1402,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1593,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1642,12 +1646,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1766,7 +1770,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1875,17 +1879,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1989,22 +1993,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,22 +2112,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2338,22 +2342,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2462,12 +2466,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2591,7 +2595,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2810,18 +2814,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,22 +2933,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3059,7 +3067,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3163,22 +3171,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3401,22 +3409,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3719,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3811,24 +3819,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3838,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3887,12 +3895,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3920,32 +3928,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3953,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3977,37 +3989,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4047,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -4068,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4092,17 +4108,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4112,17 +4128,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4150,32 +4166,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4183,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4207,37 +4227,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4265,32 +4285,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4298,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4322,37 +4346,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4380,32 +4404,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4413,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4437,17 +4465,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4457,12 +4485,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4495,32 +4523,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4528,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4552,33 +4584,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4606,32 +4642,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4639,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4663,37 +4703,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4721,32 +4761,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4754,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4778,37 +4822,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4923,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4951,32 +4995,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4984,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5008,37 +5056,37 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5153,7 +5201,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5276,22 +5324,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5329,7 +5377,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5343,47 +5391,852 @@
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>14/18</t>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1517,17 +1517,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1874,17 +1874,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2943,12 +2943,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,22 +4004,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,22 +4242,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4652,24 +4652,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5005,24 +5005,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5229,32 +5229,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5262,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5286,32 +5290,32 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5344,32 +5348,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5377,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5401,37 +5409,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5459,32 +5467,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5492,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5516,32 +5528,32 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5574,32 +5586,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5607,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5631,37 +5647,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5689,32 +5705,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5722,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5746,32 +5766,32 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5837,7 +5857,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5952,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6001,12 +6021,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6067,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6121,7 +6141,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6202,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6231,12 +6251,587 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1522,17 +1522,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2122,12 +2122,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,22 +2814,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,17 +2933,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,22 +3171,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3652,17 +3652,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4599,22 +4599,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4718,17 +4718,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,22 +4837,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5310,17 +5310,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5596,24 +5596,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5715,24 +5715,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5824,32 +5824,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5857,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5881,37 +5885,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5939,32 +5943,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5972,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5996,32 +6004,32 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6054,32 +6062,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6087,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6111,37 +6123,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6241,7 +6253,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6284,32 +6296,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6317,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6341,17 +6357,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6361,17 +6377,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6486,7 +6502,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6662,7 +6678,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6711,7 +6727,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6777,7 +6793,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6826,12 +6842,587 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1874,22 +1874,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2347,17 +2347,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2819,17 +2819,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,22 +4123,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,17 +4247,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4366,17 +4366,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,17 +4604,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4847,12 +4847,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5543,22 +5543,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5667,17 +5667,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5786,17 +5786,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5905,17 +5905,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6072,24 +6072,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6530,32 +6530,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6563,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6587,37 +6591,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6645,32 +6649,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6678,7 +6686,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6702,17 +6710,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6722,17 +6730,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6760,32 +6768,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6793,7 +6805,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6817,17 +6829,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6837,17 +6849,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6875,32 +6887,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6908,7 +6924,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6932,17 +6948,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6952,17 +6968,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7138,7 +7154,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7187,12 +7203,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7269,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7307,7 +7323,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7384,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7426,6 +7442,577 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1407,17 +1407,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,22 +2112,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,22 +2933,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,17 +4242,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,22 +4361,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4718,22 +4718,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq21推进至seq35，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4921,10 +4921,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>物理seq15（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq15映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4952,7 +4964,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4967,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5076,17 +5088,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5126,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程24%处后消失；随后反向物理轨迹由seq25推进至seq28，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -5147,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5155,10 +5167,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="inlineStr"/>
-      <c r="T40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq11映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5186,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5201,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5320,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5504,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5558,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5662,17 +5686,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5742,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5781,22 +5805,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5900,7 +5924,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5910,12 +5934,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5980,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6019,22 +6043,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6143,12 +6167,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6214,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6258,17 +6282,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6387,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6567,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6621,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6659,12 +6683,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -6686,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6725,17 +6749,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6778,24 +6802,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6805,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6844,22 +6868,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6897,24 +6921,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6924,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6963,7 +6987,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6973,12 +6997,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7030,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7039,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7063,37 +7091,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7121,32 +7149,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7154,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7178,17 +7210,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7198,12 +7230,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7269,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7351,32 +7383,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7384,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7408,17 +7444,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7428,17 +7464,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7614,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7668,7 +7704,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7840,7 +7876,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7894,7 +7930,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7955,7 +7991,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8013,6 +8049,1041 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>84.8</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1998,17 +1998,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,17 +4009,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程24%处后消失；随后反向物理轨迹由seq25推进至seq28，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程24%处后消失；随后反向物理轨迹由seq25推进至seq38，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,17 +5453,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6516,17 +6516,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7268,32 +7268,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7301,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7325,17 +7329,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7345,17 +7349,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7393,12 +7397,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -7420,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7459,7 +7463,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7469,12 +7473,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7502,32 +7506,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7535,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7559,17 +7567,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7579,17 +7587,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7704,7 +7712,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7876,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7930,7 +7938,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8106,7 +8114,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8160,7 +8168,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8336,7 +8344,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8451,7 +8459,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8505,7 +8513,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8574,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8681,7 +8689,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8796,7 +8804,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8911,7 +8919,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9026,7 +9034,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9084,6 +9092,236 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1517,22 +1517,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1874,22 +1874,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3290,17 +3290,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,22 +3647,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,22 +4123,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,17 +4242,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,22 +5567,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,17 +5686,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6396,22 +6396,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6630,22 +6630,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6749,17 +6749,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7625,32 +7625,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7658,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7682,37 +7686,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7812,7 +7816,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7851,32 +7855,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7884,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7908,37 +7916,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7966,32 +7974,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7999,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8023,32 +8035,32 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8081,32 +8093,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8114,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8138,32 +8154,32 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8229,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8311,32 +8327,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -8344,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8368,17 +8388,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8388,17 +8408,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8513,7 +8533,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8594,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8689,7 +8709,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8743,7 +8763,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8824,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8858,7 +8878,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8939,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9034,7 +9054,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9149,7 +9169,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9264,7 +9284,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9322,6 +9342,807 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>85.6</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>90.8</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1636,22 +1636,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,22 +2112,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,22 +2461,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,22 +2699,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,22 +2814,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,22 +2933,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3052,22 +3052,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,22 +3885,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,22 +4361,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4480,22 +4480,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4599,22 +4599,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4718,22 +4718,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4964,22 +4964,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,22 +5805,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,22 +5924,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,22 +6043,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6868,22 +6868,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6987,22 +6987,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8103,24 +8103,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8212,32 +8212,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8245,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8269,37 +8273,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8337,12 +8341,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -8364,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8403,22 +8407,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8446,32 +8450,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8479,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8503,37 +8511,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8561,32 +8569,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8594,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8618,37 +8630,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8676,32 +8688,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8709,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8733,37 +8749,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8791,32 +8807,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8824,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8848,37 +8868,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8939,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8978,7 +8998,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -8993,7 +9013,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9021,32 +9041,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9054,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9078,37 +9102,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9169,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9284,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9323,7 +9347,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9338,7 +9362,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9399,7 +9423,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9514,7 +9538,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9568,7 +9592,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9629,7 +9653,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9744,7 +9768,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9798,7 +9822,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9883,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9970,7 +9994,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10085,7 +10109,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10134,12 +10158,1047 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
           <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1522,17 +1522,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1993,17 +1993,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,22 +3171,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3652,17 +3652,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,17 +4004,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,22 +4837,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,22 +6162,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6511,17 +6511,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7225,22 +7225,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7344,22 +7344,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7582,17 +7582,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7706,17 +7706,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9160,32 +9160,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9193,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9217,37 +9221,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9362,7 +9366,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9390,32 +9394,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9423,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9447,37 +9455,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -9505,32 +9513,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9538,7 +9550,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9562,32 +9574,32 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9620,32 +9632,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9653,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9677,17 +9693,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9697,17 +9713,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9807,7 +9823,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9822,7 +9838,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9922,7 +9938,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9994,7 +10010,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10033,7 +10049,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10109,7 +10125,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10163,7 +10179,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10240,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10278,7 +10294,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10355,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10378,7 +10394,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10393,7 +10409,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10470,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10508,7 +10524,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10585,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10623,7 +10639,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10700,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10738,7 +10754,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10799,7 +10815,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10853,7 +10869,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10871,7 +10887,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -10914,7 +10930,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10928,7 +10944,7 @@
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="V89" s="2" t="inlineStr">
@@ -10968,7 +10984,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10976,22 +10992,22 @@
       <c r="A90" s="2" t="inlineStr"/>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -11024,12 +11040,12 @@
       <c r="M90" s="2" t="inlineStr"/>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11068,22 +11084,22 @@
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11091,22 +11107,22 @@
       <c r="A91" s="2" t="inlineStr"/>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -11139,12 +11155,12 @@
       <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11158,7 +11174,7 @@
       <c r="T91" s="2" t="inlineStr"/>
       <c r="U91" s="2" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="V91" s="2" t="inlineStr">
@@ -11183,22 +11199,823 @@
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA91" s="2" t="inlineStr">
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>84.8</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>85.6</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB91" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="AC91" s="2" t="inlineStr">
-        <is>
-          <t>7/18</t>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2347,17 +2347,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2819,17 +2819,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3052,22 +3052,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,17 +4247,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4366,17 +4366,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,17 +4604,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4964,22 +4964,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5691,17 +5691,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5810,17 +5810,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5929,17 +5929,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6754,17 +6754,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6873,17 +6873,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6992,17 +6992,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8174,17 +8174,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8531,17 +8531,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8645,22 +8645,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8888,17 +8888,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10092,32 +10092,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10125,7 +10129,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10149,17 +10153,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10169,17 +10173,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10244,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10279,7 +10283,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10294,7 +10298,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10359,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10409,7 +10413,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10437,32 +10441,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10470,7 +10478,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10494,17 +10502,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10514,17 +10522,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10552,32 +10560,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10585,7 +10597,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10609,37 +10621,37 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10712,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10739,7 +10751,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10754,7 +10766,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10782,32 +10794,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10815,7 +10831,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10839,17 +10855,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10859,17 +10875,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10930,7 +10946,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10984,7 +11000,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11061,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11084,7 +11100,7 @@
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
@@ -11099,7 +11115,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11176,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11214,7 +11230,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11291,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11329,7 +11345,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11406,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11429,7 +11445,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11505,7 +11521,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11559,7 +11575,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11567,22 +11583,22 @@
       <c r="A95" s="2" t="inlineStr"/>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -11615,12 +11631,12 @@
       <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11634,7 +11650,7 @@
       <c r="T95" s="2" t="inlineStr"/>
       <c r="U95" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="V95" s="2" t="inlineStr">
@@ -11659,22 +11675,18 @@
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB95" s="2" t="inlineStr">
-        <is>
-          <t>85.6</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr"/>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11682,22 +11694,22 @@
       <c r="A96" s="2" t="inlineStr"/>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -11730,12 +11742,12 @@
       <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11749,7 +11761,7 @@
       <c r="T96" s="2" t="inlineStr"/>
       <c r="U96" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="V96" s="2" t="inlineStr">
@@ -11774,18 +11786,22 @@
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB96" s="2" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>85.6</t>
+        </is>
+      </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11819,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -11846,7 +11862,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11860,7 +11876,7 @@
       <c r="T97" s="2" t="inlineStr"/>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="V97" s="2" t="inlineStr">
@@ -11900,7 +11916,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11918,7 +11934,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -11961,7 +11977,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11975,7 +11991,7 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
@@ -12016,6 +12032,581 @@
       <c r="AC98" s="2" t="inlineStr">
         <is>
           <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>96.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1879,17 +1879,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1998,17 +1998,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2232,13 +2232,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2466,17 +2470,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2660,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2714,7 +2718,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2829,7 +2833,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3013,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3057,12 +3061,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3132,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3251,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3290,17 +3294,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3370,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3662,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3846,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3889,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3900,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,17 +4013,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4128,17 +4132,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4380,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4485,17 +4489,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4614,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4798,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4913,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4969,12 +4973,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5044,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5159,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5344,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,17 +5457,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5572,17 +5576,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6123,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6238,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6411,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6516,17 +6520,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6635,17 +6639,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7002,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7186,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7305,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7424,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7543,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7587,17 +7591,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7821,13 +7825,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7936,17 +7944,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8050,17 +8058,17 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8249,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8288,7 +8296,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8303,7 +8311,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8422,7 +8430,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8549,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8650,12 +8658,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8725,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8769,17 +8777,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8898,7 +8906,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9078,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9197,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9312,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9431,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9550,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9594,17 +9602,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9731,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9828,17 +9836,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9943,13 +9951,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB80" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10022,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10049,17 +10061,17 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10244,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10283,7 +10295,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10298,7 +10310,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10371,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10413,7 +10425,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10544,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10609,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10641,12 +10653,12 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10679,32 +10691,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10712,7 +10728,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10736,17 +10752,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10756,17 +10772,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -10831,7 +10847,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10885,7 +10901,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10946,7 +10962,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11061,7 +11077,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11176,7 +11192,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11291,7 +11307,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11406,7 +11422,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11488,32 +11504,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11521,7 +11541,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11545,17 +11565,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11565,17 +11585,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11603,32 +11623,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11636,7 +11660,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11660,17 +11684,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11680,13 +11704,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB95" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11714,32 +11742,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11747,7 +11779,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11771,17 +11803,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11791,17 +11823,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11894,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11916,7 +11948,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11944,32 +11976,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -11977,7 +12013,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12001,32 +12037,32 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12059,32 +12095,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -12092,7 +12132,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12116,17 +12156,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12136,12 +12176,12 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12207,7 +12247,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12246,7 +12286,7 @@
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA100" s="2" t="inlineStr">
@@ -12261,7 +12301,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12362,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12366,17 +12406,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -12437,7 +12477,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12509,7 +12549,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -12552,7 +12592,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12566,7 +12606,7 @@
       <c r="T103" s="2" t="inlineStr"/>
       <c r="U103" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="V103" s="2" t="inlineStr">
@@ -12607,6 +12647,236 @@
       <c r="AC103" s="2" t="inlineStr">
         <is>
           <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC105"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2589,17 +2589,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3894,17 +3894,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4484,17 +4484,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7353,17 +7353,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8301,17 +8301,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8430,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8772,17 +8772,17 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9483,17 +9483,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9961,7 +9961,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,17 +10300,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10425,7 +10425,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10767,17 +10767,17 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA87" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11121,17 +11121,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11422,7 +11422,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11466,17 +11466,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11714,7 +11714,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11948,7 +11948,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11976,36 +11976,32 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -12013,7 +12009,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12037,17 +12033,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12057,12 +12053,12 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12105,12 +12101,12 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
@@ -12132,7 +12128,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12181,12 +12177,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -12214,32 +12210,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12247,7 +12247,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12271,17 +12271,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12291,17 +12291,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -12329,32 +12329,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12362,7 +12366,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12386,32 +12390,32 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA101" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
@@ -12444,32 +12448,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12477,7 +12485,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12501,17 +12509,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12521,17 +12529,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -12559,32 +12567,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12592,7 +12604,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12616,17 +12628,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12636,17 +12648,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12676,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -12707,7 +12719,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12721,7 +12733,7 @@
       <c r="T104" s="2" t="inlineStr"/>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
@@ -12751,12 +12763,12 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
@@ -12822,7 +12834,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12866,17 +12878,132 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>98.6</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东78路.xlsx
+++ b/data/export/2026-10-27-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3894,17 +3894,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8301,17 +8301,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,17 +10300,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11471,12 +11471,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12247,7 +12247,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12291,17 +12291,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12577,24 +12577,24 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12653,12 +12653,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12801,32 +12801,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12834,7 +12838,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12858,17 +12862,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12878,17 +12882,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12949,7 +12953,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
